--- a/output/roomself_excel/631.xlsx
+++ b/output/roomself_excel/631.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72371</v>
+        <v>136272</v>
       </c>
       <c r="D2" t="n">
-        <v>2160</v>
+        <v>3092</v>
       </c>
       <c r="E2" t="n">
-        <v>247</v>
+        <v>523</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>348056</v>
+        <v>289080</v>
       </c>
       <c r="D3" t="n">
-        <v>6016</v>
+        <v>4388</v>
       </c>
       <c r="E3" t="n">
-        <v>1540</v>
+        <v>657</v>
       </c>
       <c r="F3" t="n">
-        <v>863</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>136272</v>
+        <v>105187</v>
       </c>
       <c r="D4" t="n">
-        <v>3092</v>
+        <v>2608</v>
       </c>
       <c r="E4" t="n">
-        <v>523</v>
+        <v>359</v>
       </c>
       <c r="F4" t="n">
-        <v>294</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>105187</v>
+        <v>102093</v>
       </c>
       <c r="D5" t="n">
-        <v>2608</v>
+        <v>2724</v>
       </c>
       <c r="E5" t="n">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18112</v>
+        <v>100994</v>
       </c>
       <c r="D6" t="n">
-        <v>1212</v>
+        <v>2720</v>
       </c>
       <c r="E6" t="n">
-        <v>224</v>
+        <v>343</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31680</v>
+        <v>26958</v>
       </c>
       <c r="D7" t="n">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="E7" t="n">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>102093</v>
+        <v>58976</v>
       </c>
       <c r="D8" t="n">
-        <v>2724</v>
+        <v>2212</v>
       </c>
       <c r="E8" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23256</v>
+        <v>13884</v>
       </c>
       <c r="D9" t="n">
-        <v>1228</v>
+        <v>980</v>
       </c>
       <c r="E9" t="n">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100994</v>
+        <v>18112</v>
       </c>
       <c r="D10" t="n">
-        <v>2720</v>
+        <v>1212</v>
       </c>
       <c r="E10" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26958</v>
+        <v>23256</v>
       </c>
       <c r="D11" t="n">
-        <v>1428</v>
+        <v>1228</v>
       </c>
       <c r="E11" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26460</v>
+        <v>56549</v>
       </c>
       <c r="D12" t="n">
-        <v>1308</v>
+        <v>1944</v>
       </c>
       <c r="E12" t="n">
-        <v>147</v>
+        <v>316</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>56549</v>
+        <v>72371</v>
       </c>
       <c r="D13" t="n">
-        <v>1944</v>
+        <v>2160</v>
       </c>
       <c r="E13" t="n">
-        <v>316</v>
+        <v>247</v>
       </c>
       <c r="F13" t="n">
-        <v>213</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -730,17 +730,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13884</v>
+        <v>31680</v>
       </c>
       <c r="D14" t="n">
-        <v>980</v>
+        <v>1424</v>
       </c>
       <c r="E14" t="n">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
@@ -756,15 +756,37 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>26460</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E15" t="n">
+        <v>147</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>33172</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>1648</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>300</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>178</v>
       </c>
     </row>

--- a/output/roomself_excel/631.xlsx
+++ b/output/roomself_excel/631.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3092</v>
       </c>
-      <c r="E2" t="n">
-        <v>523</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>294</v>
+        <v>501</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>272</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>4388</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>657</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>22</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>2608</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>359</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>23</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>2724</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>322</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>20</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +623,27 @@
       <c r="D6" t="n">
         <v>2720</v>
       </c>
-      <c r="E6" t="n">
-        <v>343</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>89</v>
+        <v>69</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>321</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +661,20 @@
       <c r="D7" t="n">
         <v>1428</v>
       </c>
-      <c r="E7" t="n">
-        <v>111</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,12 @@
       <c r="D8" t="n">
         <v>2212</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +713,20 @@
       <c r="D9" t="n">
         <v>980</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>156</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>22</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +743,12 @@
       <c r="D10" t="n">
         <v>1212</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +765,12 @@
       <c r="D11" t="n">
         <v>1228</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +787,27 @@
       <c r="D12" t="n">
         <v>1944</v>
       </c>
-      <c r="E12" t="n">
-        <v>316</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>213</v>
+        <v>193</v>
+      </c>
+      <c r="G12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>293</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +825,20 @@
       <c r="D13" t="n">
         <v>2160</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>247</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>23</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +855,20 @@
       <c r="D14" t="n">
         <v>1424</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>176</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>22</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +885,20 @@
       <c r="D15" t="n">
         <v>1308</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>147</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>22</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +915,27 @@
       <c r="D16" t="n">
         <v>1648</v>
       </c>
-      <c r="E16" t="n">
-        <v>300</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>178</v>
+        <v>223</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>256</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
